--- a/XlsxSharp.Tests/Resource/Examples/Styles/StyleRowsColumns.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/Styles/StyleRowsColumns.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Style Rows and Columns" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Style Rows and Columns" sheetId="1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -393,40 +393,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:E6"/>
-  <x:sheetFormatPr defaultColWidth="5.710625" defaultRowHeight="20" customHeight="1"/>
-  <x:cols>
-    <x:col min="1" max="2" width="5.710625" style="1" customWidth="1"/>
-    <x:col min="3" max="4" width="5.710625" style="3" customWidth="1"/>
-    <x:col min="5" max="5" width="5.710625" style="6" customWidth="1"/>
-    <x:col min="6" max="16384" width="5.710625" style="1" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="2" spans="1:5" s="2" customFormat="1">
-      <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
-      <x:c r="E2" s="6"/>
-    </x:row>
-    <x:row r="3" spans="1:5" s="2" customFormat="1">
-      <x:c r="C3" s="3"/>
-      <x:c r="D3" s="3"/>
-      <x:c r="E3" s="6"/>
-    </x:row>
-    <x:row r="5" spans="1:5" s="4" customFormat="1">
-      <x:c r="E5" s="6"/>
-    </x:row>
-    <x:row r="6" spans="1:5" s="5" customFormat="1">
-      <x:c r="E6" s="6"/>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="20" customHeight="1" defaultColWidth="5.710625"/>
+  <cols>
+    <col min="1" max="2" style="1" customWidth="1" width="5.710625"/>
+    <col min="3" max="4" style="3" customWidth="1" width="5.710625"/>
+    <col min="5" max="5" style="6" customWidth="1" width="5.710625"/>
+    <col min="6" max="16384" style="1" customWidth="1" width="5.710625"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" s="2" customFormat="1">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="5" spans="1:5" s="4" customFormat="1">
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="1:5" s="5" customFormat="1">
+      <c r="E6" s="6"/>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>